--- a/static/standards-correlations/Wisconsin_CS1_State_Standards.xlsx
+++ b/static/standards-correlations/Wisconsin_CS1_State_Standards.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Crosswalk'!$A$4:$I$23</definedName>
@@ -550,10 +550,11 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scored against full lab bodies | C and Python tracks | Discovery Projects | Adopted December 2025 - the 2017 standards are superseded</t>
-        </is>
-      </c>
-    </row>
+          <t>Scored against full lab bodies | C and Python tracks | Introductory Projects | Adopted December 2025 - the 2017 standards are superseded</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -587,7 +588,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Discovery Projects</t>
+          <t>Introductory Projects</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -644,7 +645,7 @@
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>Four of six indicators are met in core. Abstraction and encapsulation for clarity and reusability is Unit 3.3's whole purpose. Developing algorithms that solve real-world problems with authenticity is structural - every lab solves a physical task on real hardware. Justifying algorithmic decisions is met by Unit 5.2's reflection on when an else-if chain beats separate ifs, plus Twenty reflection prompts across the labs require students to justify a choice or name a trade-off. NOT MET: visual modelling in flowcharts or pseudocode at high school level appears only in Discovery Systems 4 and Ext 1.2B (Dependency Map), not in the C or Python core; and DETERMINISTIC AGAINST PROBABILISTIC ALGORITHMS is absent - Ext 1.1E (Blocks vs. Text) and Ext 1.3E's rand() are the nearest, and neither names the distinction.</t>
+          <t>Four of six indicators are met in core. Abstraction and encapsulation for clarity and reusability is Unit 3.3's whole purpose. Developing algorithms that solve real-world problems with authenticity is structural - every lab solves a physical task on real hardware. Justifying algorithmic decisions is met by Unit 5.2's reflection on when an else-if chain beats separate ifs, plus Twenty reflection prompts across the labs require students to justify a choice or name a trade-off. NOT MET: visual modelling in flowcharts or pseudocode at high school level appears only in Introductory Systems 4 and Ext 1.2B (Dependency Map), not in the C or Python core; and DETERMINISTIC AGAINST PROBABILISTIC ALGORITHMS is absent - Ext 1.1E (Blocks vs. Text) and Ext 1.3E's rand() are the nearest, and neither names the distinction.</t>
         </is>
       </c>
     </row>
@@ -691,7 +692,7 @@
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>Extension-weighted and missing the accessibility half. Designing for an unfamiliar user is core in Unit 3.3, which requires documentation written for someone who has never seen the code; the feedback loop itself is optional, in Ext 3.3B (partner trades the library) and Ext 3.3F (Ready for Strangers?). Potential harms is well served: Ext 5.2D (Should It Exist?) requires a credible-source judgment on whether a deployed system should exist, Ext 5.3D (Who's Left Out?) asks who it excludes, and Discovery Systems 12 asks whose job it is to anticipate harm. ACCESSIBILITY AND DESIGNING FOR USERS WITH DISABILITIES is not addressed - the single most common gap across this entire series.</t>
+          <t>Extension-weighted and missing the accessibility half. Designing for an unfamiliar user is core in Unit 3.3, which requires documentation written for someone who has never seen the code; the feedback loop itself is optional, in Ext 3.3B (partner trades the library) and Ext 3.3F (Ready for Strangers?). Potential harms is well served: Ext 5.2D (Should It Exist?) requires a credible-source judgment on whether a deployed system should exist, Ext 5.3D (Who's Left Out?) asks who it excludes, and Introductory Systems 12 asks whose job it is to anticipate harm. ACCESSIBILITY AND DESIGNING FOR USERS WITH DISABILITIES is not addressed - the single most common gap across this entire series.</t>
         </is>
       </c>
     </row>
@@ -785,7 +786,7 @@
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>The evaluation half is core and genuinely strong; the redesign half is absent. Nineteen reflection prompts address responsibility for automated-system errors (navigation misroute, spam misflag, freight misclassification). Unit 1.1 works through a navigation app routing a driver into a wall and asks who wrote the instructions that caused it; Discovery Coding 13 asks whether a misplacement was the robot's mistake or the programmer's. Ext 5.3D (Who's Left Out?) and Ext 5.2D (Should It Exist?) carry the equity and should-it-exist questions. NOT MET: students never REDESIGN an algorithm specifically to address fairness, accessibility, or bias, and probabilistic models are absent.</t>
+          <t>The evaluation half is core and genuinely strong; the redesign half is absent. Nineteen reflection prompts address responsibility for automated-system errors (navigation misroute, spam misflag, freight misclassification). Unit 1.1 works through a navigation app routing a driver into a wall and asks who wrote the instructions that caused it; Introductory Coding 13 asks whether a misplacement was the robot's mistake or the programmer's. Ext 5.3D (Who's Left Out?) and Ext 5.2D (Should It Exist?) carry the equity and should-it-exist questions. NOT MET: students never REDESIGN an algorithm specifically to address fairness, accessibility, or bias, and probabilistic models are absent.</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1205,7 @@
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>Wisconsin names ROBOTICS in the first indicator, and this curriculum is that indicator - students use digital tools to solve problems on a physical robot for 25 labs. Structured diagnosis is core (Unit 1.1's debugging process; Discovery Coding 3 asks what two things to check first when nothing moves). TROUBLESHOOTING GUIDES: Ext 5.1G (Write the Guide) has students write a guide others could follow, and Ext 3.1E (Computer vs. Peripheral) separates processor, memory, and peripherals - both Extension-only. NOT MET: operating systems and how they manage memory, storage, and devices; evaluating and comparing computer systems or software platforms against task requirements; and system security.</t>
+          <t>Wisconsin names ROBOTICS in the first indicator, and this curriculum is that indicator - students use digital tools to solve problems on a physical robot for 25 labs. Structured diagnosis is core (Unit 1.1's debugging process; Introductory Coding 3 asks what two things to check first when nothing moves). TROUBLESHOOTING GUIDES: Ext 5.1G (Write the Guide) has students write a guide others could follow, and Ext 3.1E (Computer vs. Peripheral) separates processor, memory, and peripherals - both Extension-only. NOT MET: operating systems and how they manage memory, storage, and devices; evaluating and comparing computer systems or software platforms against task requirements; and system security.</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1252,7 @@
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>The weakest concept in the file, and consistent with every other state. Ext 5.3F (Talking to a Server) traces a file from the student's machine across the internet to a remote server and asks what has to go right - address routing, server uptime, the local connection - which touches the third indicator loosely. Discovery Systems 9 covers senders, receivers, and protocols. NOT MET: routers, cables, and switches by name; network topology and visual network models; and any comparison of network types by structure, performance, or scalability. Network hardware is a documented recurring gap for this curriculum.</t>
+          <t>The weakest concept in the file, and consistent with every other state. Ext 5.3F (Talking to a Server) traces a file from the student's machine across the internet to a remote server and asks what has to go right - address routing, server uptime, the local connection - which touches the third indicator loosely. Introductory Systems 9 covers senders, receivers, and protocols. NOT MET: routers, cables, and switches by name; network topology and visual network models; and any comparison of network types by structure, performance, or scalability. Network hardware is a documented recurring gap for this curriculum.</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1342,7 @@
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>Two indicators land well. PERSONAL DATA COLLECTION: Ext 2.6E (Automatic Data Collection) makes automatic collection concrete from inside a system the student built. RULES AND POLICIES: Ext 5.3E (Ethical Use and the Rules) names the school Acceptable Use Policy directly and asks what it permits, alongside Lab 5.3 core teaches the MIT License by name: what it permits and the single condition it imposes. - so acceptable use and copyright are both covered, though COPPA is not. Responsible and harmful uses are covered through Discovery Systems 12 and Ext 5.2D (Should It Exist?). NOT MET: surveillance and recommendation systems, the ENVIRONMENTAL and economic impact of computing infrastructure, and global technology use across cultures.</t>
+          <t>Two indicators land well. PERSONAL DATA COLLECTION: Ext 2.6E (Automatic Data Collection) makes automatic collection concrete from inside a system the student built. RULES AND POLICIES: Ext 5.3E (Ethical Use and the Rules) names the school Acceptable Use Policy directly and asks what it permits, alongside Lab 5.3 core teaches the MIT License by name: what it permits and the single condition it imposes. - so acceptable use and copyright are both covered, though COPPA is not. Responsible and harmful uses are covered through Introductory Systems 12 and Ext 5.2D (Should It Exist?). NOT MET: surveillance and recommendation systems, the ENVIRONMENTAL and economic impact of computing infrastructure, and global technology use across cultures.</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1385,7 @@
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>One of four indicators, Extension-only and weak. Ext 5.3E (Ethical Use and the Rules) asks whether there should be a law requiring publicly posted code to carry a license, which is evaluating a policy intended to encourage ethical practice - the fourth indicator, in miniature. THE OTHER THREE ARE ENTIRELY ABSENT: the history of computing, early computing devices, the contributions of named individuals and underrepresented groups, and the environmental effects of historical innovations appear nowhere in either track or in the Discovery projects. This matches the Virginia CSF.IC.3 finding exactly and is the cheapest gap in the series to close - a single reading-and-reflection Extension would carry most of it.</t>
+          <t>One of four indicators, Extension-only and weak. Ext 5.3E (Ethical Use and the Rules) asks whether there should be a law requiring publicly posted code to carry a license, which is evaluating a policy intended to encourage ethical practice - the fourth indicator, in miniature. THE OTHER THREE ARE ENTIRELY ABSENT: the history of computing, early computing devices, the contributions of named individuals and underrepresented groups, and the environmental effects of historical innovations appear nowhere in either track or in the Introductory projects. This matches the Virginia CSF.IC.3 finding exactly and is the cheapest gap in the series to close - a single reading-and-reflection Extension would carry most of it.</t>
         </is>
       </c>
     </row>
@@ -1508,6 +1509,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
@@ -1552,7 +1554,7 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>Discovery Project, Coding strand, project NN (01-17).</t>
+          <t>Introductory Project, Coding strand, project NN (01-17).</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1566,7 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Discovery Project, Systems strand, project NN (01-14).</t>
+          <t>Introductory Project, Systems strand, project NN (01-14).</t>
         </is>
       </c>
     </row>
@@ -1700,6 +1702,8 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
@@ -1727,7 +1731,7 @@
 WRITING COMMITTEE NOTE: the 2025 standards were written by a committee co-chaired by Dennis Brylow (Marquette University) and Tina Lemmens (CESA 7), with nine members drawn largely from Wisconsin high schools. Wisconsin's vision statement explicitly names artificial intelligence, data science, cybersecurity, and software development as specialized facets students should be able to study.
 Crosswalk analysis (c) KIPR / Botball Explorer.
 === METHODOLOGY (revised) ===
-Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Discovery projects.
+Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Introductory projects.
 Scoring rule: Full requires evidence in the core lab flow. Partial is assigned where the only evidence sits in an optional Extension Challenge (labelled 'Finished early?'), or where the standard is only partly met.
 RESULT: 2 Full, 17 Partial, 0 blank of 19 standards - but see the SCORING GRAIN note above before quoting that. Zero blanks across 19 standards covering 88 indicators is the substantive finding: there is no Wisconsin standard this curriculum fails to touch at all.
   Strongest: ALG.3 (problem solving) and PRO.1 (programming fundamentals) - Full, all indicators met.
